--- a/stories/arbres/ATOM-JEU.REG.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam et papa jouent au jeu de l'oie. Les pions sont lisses. Papa arrive le premier. Papa a gagné. Adam sent un nœud dans le ventre. Papa dit : l'autre peut gagner. C'est le jeu. Adam dit : je suis déçu. Papa dit : être déçu, c'est permis. Adam souffle. Il dit : bravo papa. Papa sourit. Papa dit : on peut rejouer plus tard. Adam hoche la tête. Il va boire de l'eau. Plus tard, au jardin, Adam joue aux quilles avec maman. Maman fait tomber plus de quilles. Maman a gagné. Adam sent encore le nœud. Il se souvient. L'autre peut gagner. Il dit : je suis déçu. Être déçu, c'est permis. Il dit : bravo maman. Maman dit : on rejoue plus tard. D'abord, on range. Adam empile les quilles. Après le goûter, ils rejouent. Adam sourit. Même leçon, autre jeu. Perdre un tour, ce n'est pas grave. On dit bravo. On rejoue plus tard.</t>
+          <t>Adam et papa jouent au jeu de l'oie. Les pions sont lisses. Papa arrive le premier. Papa a gagné. Adam sent un nœud dans le ventre. L'autre peut gagner. C'est le jeu. Je suis déçu. Être déçu, c'est permis. Adam souffle. Bravo papa. Papa sourit. On peut rejouer plus tard. Adam hoche la tête. Il va boire de l'eau. Plus tard, au jardin, Adam joue aux quilles avec maman. Maman fait tomber plus de quilles. Maman a gagné. Adam sent encore le nœud. Il se souvient. L'autre peut gagner. Je suis déçu. Être déçu, c'est permis. Bravo maman. On rejoue plus tard. D'abord, on range. Adam empile les quilles. Après le goûter, ils rejouent. Adam sourit. Même leçon, autre jeu. Perdre un tour, ce n'est pas grave. On dit bravo. On rejoue plus tard.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,22 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Adam et papa jouent au jeu de l'oie. Les pions sont lisses. Papa arrive le premier. Papa a gagné. Adam sent un nœud dans le ventre.
+papa|L'autre peut gagner. C'est le jeu.
+enfant-m|Je suis déçu.
+papa|Être déçu, c'est permis.
+narrateur|Adam souffle.
+narrateur|Bravo papa. Papa sourit.
+papa|On peut rejouer plus tard.
+narrateur|Adam hoche la tête. Il va boire de l'eau. Plus tard, au jardin, Adam joue aux quilles avec maman. Maman fait tomber plus de quilles. Maman a gagné. Adam sent encore le nœud. Il se souvient. L'autre peut gagner.
+narrateur|Je suis déçu. Être déçu, c'est permis.
+narrateur|Bravo maman.
+maman|On rejoue plus tard. D'abord, on range.
+narrateur|Adam empile les quilles. Après le goûter, ils rejouent. Adam sourit. Même leçon, autre jeu. Perdre un tour, ce n'est pas grave. On dit bravo. On rejoue plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Papa a gagné. Que peut faire Adam ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Adam a nommé sa déception. C'était permis. Il a dit bravo. Ils ont rejoué plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1829,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Adam pose la dernière quille. Maman verse le goûter.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1996,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1321,6 +1326,7 @@
 narrateur|Adam empile les quilles. Après le goûter, ils rejouent. Adam sourit. Même leçon, autre jeu. Perdre un tour, ce n'est pas grave. On dit bravo. On rejoue plus tard.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Papa a gagné. Que peut faire Adam ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1678,7 @@
           <t>narrateur|Adam a nommé sa déception. C'était permis. Il a dit bravo. Ils ont rejoué plus tard.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Adam pose la dernière quille. Maman verse le goûter.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.REG.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Adam dit bravo, puis rejoue</t>
+          <t>L'oie d'Aniss, puis le jardin</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss perd au jeu de l'oie, puis aux quilles. Deux fois il dit bravo et ils rejoueront plus tard.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Adam et papa jouent au jeu de l'oie. Les pions sont lisses. Papa arrive le premier. Papa a gagné. Adam sent un nœud dans le ventre. L'autre peut gagner. C'est le jeu. Je suis déçu. Être déçu, c'est permis. Adam souffle. Bravo papa. Papa sourit. On peut rejouer plus tard. Adam hoche la tête. Il va boire de l'eau. Plus tard, au jardin, Adam joue aux quilles avec maman. Maman fait tomber plus de quilles. Maman a gagné. Adam sent encore le nœud. Il se souvient. L'autre peut gagner. Je suis déçu. Être déçu, c'est permis. Bravo maman. On rejoue plus tard. D'abord, on range. Adam empile les quilles. Après le goûter, ils rejouent. Adam sourit. Même leçon, autre jeu. Perdre un tour, ce n'est pas grave. On dit bravo. On rejoue plus tard.</t>
+          <t>Une oie peinte rit sur le couvercle. Un rayon traverse la poussière du salon. La porte de la terrasse est un peu ouverte. Un escargot a laissé un fil brillant. Les pions du jeu sont lisses et froids. Une mouche se pose sur le couvercle. Elle s'en va. L'oie reste peinte. Tu as vu l'oie, Aniss ? Oui. Elle a un bec orange. En ce moment, papa pose le plateau. Les cases sont vertes, rouges, jaunes. Aniss avance son pion, case après case. À moi. J'avance aussi. Papa arrive le premier. Je suis arrivé. J'ai gagné ce tour. Aniss sent un nœud dans le ventre. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. C'est le jeu. Aniss souffle. Il pose le pion. Bravo papa. Merci. On peut rejouer plus tard. Je vais boire de l'eau. Oui. L'eau est sur la table. Aniss boit. L'eau est fraîche. Plus tard, au jardin, l'air sent l'herbe. Maman pose des quilles sur la terre. On joue un petit tour, Aniss ? Oui, maman. Maman fait tomber plus de quilles. J'ai gagné ce tour. Aniss sent encore le nœud. Il se souvient du salon, et de l'oie. L'autre peut gagner. Je suis déçu. Être déçu, c'est permis. Bravo maman. On rejoue plus tard. D'abord, on range. Aniss empile les quilles, une par une. Après le goûter, ils rejouent un peu. Au salon, puis au jardin. Oui. Perdre un tour, ce n'est pas grave. On dit bravo. On rejoue plus tard. Tu as dit bravo deux fois, Aniss. Bravo. Tu as fait du bon travail. Aniss essuie ses mains dans l'herbe. L'herbe est un peu mouillée. Tu as dit bravo. Le nœud, c'est permis. On rejoue plus tard. Oui. Après le gâteau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,21 +1324,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Adam et papa jouent au jeu de l'oie. Les pions sont lisses. Papa arrive le premier. Papa a gagné. Adam sent un nœud dans le ventre.
-papa|L'autre peut gagner. C'est le jeu.
+          <t>narrateur|Une oie peinte rit sur le couvercle.
+narrateur|Un rayon traverse la poussière du salon.
+narrateur|La porte de la terrasse est un peu ouverte.
+narrateur|Un escargot a laissé un fil brillant.
+narrateur|Les pions du jeu sont lisses et froids.
+narrateur|Une mouche se pose sur le couvercle.
+narrateur|Elle s'en va. L'oie reste peinte.
+papa|Tu as vu l'oie, Aniss ?
+enfant-m|Oui. Elle a un bec orange.
+narrateur|En ce moment, papa pose le plateau.
+narrateur|Les cases sont vertes, rouges, jaunes.
+narrateur|Aniss avance son pion, case après case.
+papa|À moi. J'avance aussi.
+narrateur|Papa arrive le premier.
+papa|Je suis arrivé. J'ai gagné ce tour.
+narrateur|Aniss sent un nœud dans le ventre.
 enfant-m|Je suis déçu.
 papa|Être déçu, c'est permis.
-narrateur|Adam souffle.
-narrateur|Bravo papa. Papa sourit.
-papa|On peut rejouer plus tard.
-narrateur|Adam hoche la tête. Il va boire de l'eau. Plus tard, au jardin, Adam joue aux quilles avec maman. Maman fait tomber plus de quilles. Maman a gagné. Adam sent encore le nœud. Il se souvient. L'autre peut gagner.
-narrateur|Je suis déçu. Être déçu, c'est permis.
-narrateur|Bravo maman.
+papa|L'autre peut gagner. C'est le jeu.
+narrateur|Aniss souffle. Il pose le pion.
+enfant-m|Bravo papa.
+papa|Merci. On peut rejouer plus tard.
+enfant-m|Je vais boire de l'eau.
+papa|Oui. L'eau est sur la table.
+narrateur|Aniss boit. L'eau est fraîche.
+narrateur|Plus tard, au jardin, l'air sent l'herbe.
+narrateur|Maman pose des quilles sur la terre.
+maman|On joue un petit tour, Aniss ?
+enfant-m|Oui, maman.
+narrateur|Maman fait tomber plus de quilles.
+maman|J'ai gagné ce tour.
+narrateur|Aniss sent encore le nœud.
+narrateur|Il se souvient du salon, et de l'oie.
+enfant-m|L'autre peut gagner.
+enfant-m|Je suis déçu.
+maman|Être déçu, c'est permis.
+enfant-m|Bravo maman.
 maman|On rejoue plus tard. D'abord, on range.
-narrateur|Adam empile les quilles. Après le goûter, ils rejouent. Adam sourit. Même leçon, autre jeu. Perdre un tour, ce n'est pas grave. On dit bravo. On rejoue plus tard.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Aniss empile les quilles, une par une.
+narrateur|Après le goûter, ils rejouent un peu.
+enfant-m|Au salon, puis au jardin.
+maman|Oui. Perdre un tour, ce n'est pas grave.
+maman|On dit bravo. On rejoue plus tard.
+papa|Tu as dit bravo deux fois, Aniss.
+papa|Bravo. Tu as fait du bon travail.
+narrateur|Aniss essuie ses mains dans l'herbe.
+narrateur|L'herbe est un peu mouillée.
+maman|Tu as dit bravo. Le nœud, c'est permis.
+enfant-m|On rejoue plus tard.
+maman|Oui. Après le gâteau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1351,7 +1400,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Papa a gagné. Que peut faire Adam ?</t>
+          <t>Papa a gagné. Que peut faire Aniss ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,10 +1556,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Papa a gagné. Que peut faire Adam ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Papa a gagné.
+narrateur|Que peut faire Aniss ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,7 +1584,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Adam a nommé sa déception. C'était permis. Il a dit bravo. Ils ont rejoué plus tard.</t>
+          <t>Aniss a nommé sa déception. C'était permis. Il a dit bravo. Ils ont rejoué plus tard. Au salon, puis au jardin ? Oui. Bravo, puis plus tard. Bravo, Aniss. C'est du bon travail. L'escargot n'est plus sur la dalle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1675,10 +1724,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Adam a nommé sa déception. C'était permis. Il a dit bravo. Ils ont rejoué plus tard.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss a nommé sa déception.
+narrateur|C'était permis.
+narrateur|Il a dit bravo.
+narrateur|Ils ont rejoué plus tard.
+papa|Au salon, puis au jardin ?
+enfant-m|Oui. Bravo, puis plus tard.
+maman|Bravo, Aniss. C'est du bon travail.
+narrateur|L'escargot n'est plus sur la dalle.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1703,7 +1758,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Adam pose la dernière quille. Maman verse le goûter.</t>
+          <t>Aniss pose la dernière quille. Je verse le goûter. J'ai soif un peu. Voici l'eau, puis le gâteau. On a rangé le plateau, aussi. L'oie est sur le couvercle. Oui. Elle attend plus tard.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,10 +1894,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Adam pose la dernière quille. Maman verse le goûter.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Aniss pose la dernière quille.
+maman|Je verse le goûter.
+enfant-m|J'ai soif un peu.
+maman|Voici l'eau, puis le gâteau.
+papa|On a rangé le plateau, aussi.
+enfant-m|L'oie est sur le couvercle.
+papa|Oui. Elle attend plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1867,7 +1927,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le gâteau sent le citron. J'étais déçu. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Aniss. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,10 +2067,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le gâteau sent le citron.
+enfant-m|J'étais déçu. C'était permis.
+maman|Oui. Tu as dit bravo.
+papa|On rejoue plus tard.
+papa|Bravo, Aniss.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2029,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2131,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-03.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une oie peinte rit sur le couvercle. Un rayon traverse la poussière du salon. La porte de la terrasse est un peu ouverte. Un escargot a laissé un fil brillant. Les pions du jeu sont lisses et froids. Une mouche se pose sur le couvercle. Elle s'en va. L'oie reste peinte. Tu as vu l'oie, Aniss ? Oui. Elle a un bec orange. En ce moment, papa pose le plateau. Les cases sont vertes, rouges, jaunes. Aniss avance son pion, case après case. À moi. J'avance aussi. Papa arrive le premier. Je suis arrivé. J'ai gagné ce tour. Aniss sent un nœud dans le ventre. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. C'est le jeu. Aniss souffle. Il pose le pion. Bravo papa. Merci. On peut rejouer plus tard. Je vais boire de l'eau. Oui. L'eau est sur la table. Aniss boit. L'eau est fraîche. Plus tard, au jardin, l'air sent l'herbe. Maman pose des quilles sur la terre. On joue un petit tour, Aniss ? Oui, maman. Maman fait tomber plus de quilles. J'ai gagné ce tour. Aniss sent encore le nœud. Il se souvient du salon, et de l'oie. L'autre peut gagner. Je suis déçu. Être déçu, c'est permis. Bravo maman. On rejoue plus tard. D'abord, on range. Aniss empile les quilles, une par une. Après le goûter, ils rejouent un peu. Au salon, puis au jardin. Oui. Perdre un tour, ce n'est pas grave. On dit bravo. On rejoue plus tard. Tu as dit bravo deux fois, Aniss. Bravo. Tu as fait du bon travail. Aniss essuie ses mains dans l'herbe. L'herbe est un peu mouillée. Tu as dit bravo. Le nœud, c'est permis. On rejoue plus tard. Oui. Après le gâteau.</t>
+          <t>Une oie peinte rit sur le couvercle. Un rayon traverse la poussière du salon. La porte de la terrasse est un peu ouverte. Un escargot a laissé un fil brillant. Les pions du jeu sont lisses et froids. Une mouche se pose sur le couvercle. Elle s'en va. L'oie reste peinte. Tu as vu l'oie, Aniss ? Oui. Elle a un bec orange. En ce moment, papa pose le plateau. Les cases sont vertes, rouges, jaunes. Aniss avance son pion, case après case. À moi. J'avance aussi. Papa arrive le premier. Je suis arrivé. J'ai gagné ce tour. Aniss sent un nœud dans le ventre. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. C'est le jeu. Aniss souffle. Il pose le pion. Bravo papa. Merci. On peut rejouer plus tard. Je vais boire de l'eau. Oui. L'eau est sur la table. Aniss boit. L'eau est fraîche. Plus tard, au jardin, l'air sent l'herbe. Maman pose des quilles sur la terre. On joue un petit tour, Aniss ? Oui, maman. Maman fait tomber plus de quilles. J'ai gagné ce tour. Aniss sent encore le nœud. Il se souvient du salon, et de l'oie. L'autre peut gagner. Je suis déçu. Être déçu, c'est permis. Bravo maman. On rejoue plus tard. D'abord, on range. Aniss empile les quilles, une par une. Après le goûter, ils rejouent un peu. Au salon, puis au jardin. Oui. Perdre un tour, ce n'est pas grave. On dit bravo. On rejoue plus tard. Tu as dit bravo deux fois, Aniss. Aniss essuie ses mains dans l'herbe. L'herbe est un peu mouillée. Tu as dit bravo. Le nœud, c'est permis. On rejoue plus tard. Oui. Après le gâteau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam et papa jouent au jeu de l'oie. Les pions sont lisses. Papa arrive le premier. Papa a gagné. Adam sent un nœud dans le ventre. Papa dit : &lt;emphasis level="moderate"&gt;l'autre&lt;/emphasis&gt; peut gagner. C'est le jeu. Adam dit : je suis déçu. Papa dit : être déçu, c'est permis. Adam souffle. Il dit : bravo papa. Papa sourit. Papa dit : on peut rejouer plus tard. Adam hoche la tête. Il va boire de l'eau. Plus tard, au jardin, Adam joue aux quilles avec maman. Maman fait tomber plus de quilles. Maman a gagné. Adam sent encore le nœud. Il se souvient. L'autre peut gagner. Il dit : je suis déçu. Être déçu, c'est permis. Il dit : bravo maman. Maman dit : on rejoue plus tard. D'abord, on range. Adam empile les quilles. Après le goûter, ils rejouent. Adam sourit. Même leçon, autre jeu. Perdre un tour, ce n'est pas grave. On dit bravo. On rejoue plus tard.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une oie peinte rit sur le couvercle. Un rayon traverse la poussière du salon. La porte de la terrasse est un peu ouverte. Un escargot a laissé un fil brillant. Les pions du jeu sont lisses et froids. Une mouche se pose sur le couvercle. Elle s'en va. L'oie reste peinte. Tu as vu l'oie, Aniss ? Oui. Elle a un bec orange. En ce moment, papa pose le plateau. Les cases sont vertes, rouges, jaunes. Aniss avance son pion, case après case. À moi. J'avance aussi. Papa arrive le premier. Je suis arrivé. J'ai gagné ce tour. Aniss sent un nœud dans le ventre. Je suis déçu. Être déçu, c'est permis. L'autre peut gagner. C'est le jeu. Aniss souffle. Il pose le pion. Bravo papa. Merci. On peut rejouer plus tard. Je vais boire de l'eau. Oui. L'eau est sur la table. Aniss boit. L'eau est fraîche. Plus tard, au jardin, l'air sent l'herbe. Maman pose des quilles sur la terre. On joue un petit tour, Aniss ? Oui, maman. Maman fait tomber plus de quilles. J'ai gagné ce tour. Aniss sent encore le nœud. Il se souvient du salon, et de l'oie. L'autre peut gagner. Je suis déçu. Être déçu, c'est permis. Bravo maman. On rejoue plus tard. D'abord, on range. Aniss empile les quilles, une par une. Après le goûter, ils rejouent un peu. Au salon, puis au jardin. Oui. Perdre un tour, ce n'est pas grave. On dit bravo. On rejoue plus tard. Tu as dit bravo deux fois, Aniss. Aniss essuie ses mains dans l'herbe. L'herbe est un peu mouillée. Tu as dit bravo. Le nœud, c'est permis. On rejoue plus tard. Oui. Après le gâteau.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1368,7 +1368,6 @@
 maman|Oui. Perdre un tour, ce n'est pas grave.
 maman|On dit bravo. On rejoue plus tard.
 papa|Tu as dit bravo deux fois, Aniss.
-papa|Bravo. Tu as fait du bon travail.
 narrateur|Aniss essuie ses mains dans l'herbe.
 narrateur|L'herbe est un peu mouillée.
 maman|Tu as dit bravo. Le nœud, c'est permis.
@@ -1405,7 +1404,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Papa a gagné. Que peut faire Adam ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa a gagné. Que peut faire Aniss ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1584,12 +1583,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aniss a nommé sa déception. C'était permis. Il a dit bravo. Ils ont rejoué plus tard. Au salon, puis au jardin ? Oui. Bravo, puis plus tard. Bravo, Aniss. C'est du bon travail. L'escargot n'est plus sur la dalle.</t>
+          <t>Aniss a nommé sa déception. C'était permis. Il a dit bravo. Ils ont rejoué plus tard. Au salon, puis au jardin ? Oui. Bravo, puis plus tard. L'escargot n'est plus sur la dalle.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam a nommé sa déception. C'était permis. Il a dit bravo. Ils ont rejoué plus tard.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss a nommé sa déception. C'était permis. Il a dit bravo. Ils ont rejoué plus tard. Au salon, puis au jardin ? Oui. Bravo, puis plus tard. L'escargot n'est plus sur la dalle.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1730,7 +1729,6 @@
 narrateur|Ils ont rejoué plus tard.
 papa|Au salon, puis au jardin ?
 enfant-m|Oui. Bravo, puis plus tard.
-maman|Bravo, Aniss. C'est du bon travail.
 narrateur|L'escargot n'est plus sur la dalle.</t>
         </is>
       </c>
@@ -1763,7 +1761,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Adam pose la dernière quille. Maman verse le goûter.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss pose la dernière quille. Je verse le goûter. J'ai soif un peu. Voici l'eau, puis le gâteau. On a rangé le plateau, aussi. L'oie est sur le couvercle. Oui. Elle attend plus tard.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1927,12 +1925,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le gâteau sent le citron. J'étais déçu. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Aniss. L'histoire est finie.</t>
+          <t>Le gâteau sent le citron. J'étais déçu. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Aniss.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le gâteau sent le citron. J'étais déçu. C'était permis. Oui. Tu as dit bravo. On rejoue plus tard. Bravo, Aniss.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2071,8 +2069,7 @@
 enfant-m|J'étais déçu. C'était permis.
 maman|Oui. Tu as dit bravo.
 papa|On rejoue plus tard.
-papa|Bravo, Aniss.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Aniss.</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2138,6 +2135,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.001-03.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.001-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Adam, papa, maman</t>
+          <t>Aniss, papa, maman</t>
         </is>
       </c>
     </row>
